--- a/shore_crane_report.xlsx
+++ b/shore_crane_report.xlsx
@@ -756,22 +756,22 @@
         <v>14</v>
       </c>
       <c r="D8" s="3">
-        <v>0.7430555555555556</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="3">
-        <v>0.7472222222222222</v>
+        <v>0.6375</v>
       </c>
       <c r="I8" s="4">
-        <v>4.23</v>
+        <v>11.59</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>20</v>
@@ -780,7 +780,7 @@
         <v>18.25</v>
       </c>
       <c r="L8" s="1">
-        <v>115.796</v>
+        <v>211.517</v>
       </c>
       <c r="M8" s="1"/>
     </row>
@@ -795,22 +795,22 @@
         <v>14</v>
       </c>
       <c r="D9" s="3">
-        <v>0.4861111111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="3">
-        <v>0.6375</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="I9" s="4">
-        <v>11.59</v>
+        <v>4.23</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>20</v>
@@ -819,7 +819,7 @@
         <v>18.25</v>
       </c>
       <c r="L9" s="1">
-        <v>211.517</v>
+        <v>115.796</v>
       </c>
       <c r="M9" s="1"/>
     </row>
@@ -834,22 +834,22 @@
         <v>14</v>
       </c>
       <c r="D10" s="3">
-        <v>0.3409722222222222</v>
+        <v>0.7104166666666667</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="3">
-        <v>0.7069444444444445</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="I10" s="4">
-        <v>216.552</v>
+        <v>32.831</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>18</v>
@@ -858,7 +858,7 @@
         <v>29.25</v>
       </c>
       <c r="L10" s="1">
-        <v>6334.146</v>
+        <v>1440.460</v>
       </c>
       <c r="M10" s="1"/>
     </row>
@@ -873,22 +873,22 @@
         <v>14</v>
       </c>
       <c r="D11" s="3">
-        <v>0.7104166666666667</v>
+        <v>0.3409722222222222</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="3">
-        <v>0.7284722222222222</v>
+        <v>0.7069444444444445</v>
       </c>
       <c r="I11" s="4">
-        <v>32.831</v>
+        <v>216.552</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>18</v>
@@ -897,7 +897,7 @@
         <v>29.25</v>
       </c>
       <c r="L11" s="1">
-        <v>1440.460</v>
+        <v>6334.146</v>
       </c>
       <c r="M11" s="1"/>
     </row>
@@ -912,22 +912,22 @@
         <v>14</v>
       </c>
       <c r="D12" s="3">
-        <v>0.7340277777777777</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="3">
-        <v>0.7548611111111111</v>
+        <v>0.5340277777777778</v>
       </c>
       <c r="I12" s="4">
-        <v>8.619999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>20</v>
@@ -936,7 +936,7 @@
         <v>18.25</v>
       </c>
       <c r="L12" s="1">
-        <v>235.972</v>
+        <v>191.260</v>
       </c>
       <c r="M12" s="1"/>
     </row>
@@ -951,22 +951,22 @@
         <v>14</v>
       </c>
       <c r="D13" s="3">
-        <v>0.5208333333333334</v>
+        <v>0.7340277777777777</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="3">
-        <v>0.5340277777777778</v>
+        <v>0.7548611111111111</v>
       </c>
       <c r="I13" s="4">
-        <v>10.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>20</v>
@@ -975,7 +975,7 @@
         <v>18.25</v>
       </c>
       <c r="L13" s="1">
-        <v>191.260</v>
+        <v>235.972</v>
       </c>
       <c r="M13" s="1"/>
     </row>
